--- a/feasibility_outputs/profile_write_simulation/simulated_write_review.xlsx
+++ b/feasibility_outputs/profile_write_simulation/simulated_write_review.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Rollback Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Simulated Records'!$A$1:$N$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Commit Log'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rollback Plan'!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Simulated Records'!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Commit Log'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rollback Plan'!$A$1:$D$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -48,7 +48,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -59,12 +59,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00366092"/>
         <bgColor rgb="00366092"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-        <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -94,17 +88,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -476,7 +473,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -499,7 +496,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED_BY_COMMIT_GATE</t>
+          <t>SIMULATION_READY_FOR_REVIEW</t>
         </is>
       </c>
     </row>
@@ -510,7 +507,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -520,7 +517,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +527,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -594,21 +591,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
   </cols>
@@ -685,8 +682,200 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>SIM_REC_0001</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>WRITE_CANDIDATE_0001</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>CHINT</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>NXM-63S</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>MCCB Chint NXM-63S 3P 25÷63 25</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>800000</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>800000</v>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>CHINT|NXM-63S|P3|800000|MCCBCHINTNXM63S3P256325</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>INSERT_CANDIDATE</t>
+        </is>
+      </c>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>WOULD_INSERT</t>
+        </is>
+      </c>
+      <c r="N2" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>SIM_REC_0002</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>WRITE_CANDIDATE_0002</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>CHINT</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>NXM-125S</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>MCCB Chint NXM-125S 3P 80÷125 25</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>860000</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>860000</v>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>CHINT|NXM-125S|P3|860000|MCCBCHINTNXM125S3P801252</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>INSERT_CANDIDATE</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>WOULD_INSERT</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>SIM_REC_0003</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>WRITE_CANDIDATE_0003</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>CHINT</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>NXM-250S</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>MCCB Chint NXM-250S 3P 160,200,250 35</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>CHINT|NXM-250S|P3|1400000|MCCBCHINTNXM250S3P160200</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>INSERT_CANDIDATE</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>WOULD_INSERT</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:N4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -697,15 +886,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,8 +929,104 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>LOG_ENTRY_0001</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>WRITE_CANDIDATE_0001</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>CHINT|NXM-63S|P3|800000|MCCBCHINTNXM63S3P256325</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>simulation_insert</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>WOULD_INSERT</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>[WARNING: not_checked_against_master_database] Giả lập thêm mới thành công.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>LOG_ENTRY_0002</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>WRITE_CANDIDATE_0002</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>CHINT|NXM-125S|P3|860000|MCCBCHINTNXM125S3P801252</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>simulation_insert</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>WOULD_INSERT</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>[WARNING: not_checked_against_master_database] Giả lập thêm mới thành công.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>LOG_ENTRY_0003</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>WRITE_CANDIDATE_0003</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>CHINT|NXM-250S|P3|1400000|MCCBCHINTNXM250S3P160200</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>simulation_insert</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>WOULD_INSERT</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>[WARNING: not_checked_against_master_database] Giả lập thêm mới thành công.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -752,13 +1037,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -783,8 +1068,74 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>ROLLBACK_ACT_0001</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>SIM_REC_0001</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Xóa bản ghi giả lập SIM_REC_0001 đối với write_key CHINT|NXM-63S|P3|800000|MCCBCHINTNXM63S3P256325.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>ROLLBACK_ACT_0002</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>SIM_REC_0002</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Xóa bản ghi giả lập SIM_REC_0002 đối với write_key CHINT|NXM-125S|P3|860000|MCCBCHINTNXM125S3P801252.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>ROLLBACK_ACT_0003</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>SIM_REC_0003</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Xóa bản ghi giả lập SIM_REC_0003 đối với write_key CHINT|NXM-250S|P3|1400000|MCCBCHINTNXM250S3P160200.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D1"/>
+  <autoFilter ref="A1:D4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>